--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>12</v>
@@ -666,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -681,11 +681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -767,40 +767,220 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>3</v>
+      <c r="K6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -838,7 +1018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: J. Bailey (21 L)</t>
+          <t>Maior volume: J. Bailey (40 L)</t>
         </is>
       </c>
     </row>
@@ -850,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: J. Bailey (10 3PA)</t>
+          <t>Maior volume 3pt: J. Bailey (20 3PA)</t>
         </is>
       </c>
     </row>
@@ -862,7 +1042,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: P. Carvalhal (1.1 pts/shot)</t>
+          <t>Mais eficaz: D. Carr (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -874,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (25 L)</t>
+          <t>Zona mais usada: Above the Break 3 (42 L)</t>
         </is>
       </c>
     </row>
@@ -886,7 +1066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (58.8%)</t>
+          <t>Zona mais eficaz: Restricted Area (52.8%)</t>
         </is>
       </c>
     </row>
@@ -902,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1035,34 +1215,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1070,11 +1250,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1083,18 +1263,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1112,34 +1292,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1147,11 +1327,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1160,18 +1340,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1180,55 +1360,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1237,18 +1417,18 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1257,180 +1437,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,32 +1623,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1479,87 +1659,241 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_F._NETO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_M._POMBO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>7</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ESG_F._NETO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F. Neto</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1570,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1694,33 +2028,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1729,7 +2063,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1742,27 +2076,27 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1771,12 +2105,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1784,62 +2118,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>7</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1848,82 +2182,313 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>2</v>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1934,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2037,29 +2602,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2067,18 +2632,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2093,29 +2658,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2123,111 +2688,111 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2235,115 +2800,115 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2351,68 +2916,180 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_F._NETO</t>
+          <t>ESG_M._POMBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ESG_F._NETO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F. Neto</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2423,11 +3100,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2517,38 +3194,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2560,18 +3237,74 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="n">
+        <v>27</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>2</v>
+      <c r="N3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2650,17 +3383,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -2668,14 +3401,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2685,25 +3418,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2720,32 +3453,32 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2755,60 +3488,60 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2821,11 +3554,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -2835,22 +3568,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +3598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2985,11 +3718,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2998,11 +3731,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3011,31 +3744,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -3055,11 +3788,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3068,11 +3801,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3081,7 +3814,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3089,205 +3822,205 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -3299,65 +4032,65 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -3369,11 +4102,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -3385,67 +4118,207 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>ESG_J._BERTINO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_M._POMBO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>ESG_F._NETO</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>F. Neto</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3456,7 +4329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3546,7 +4419,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3556,60 +4429,60 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3622,43 +4495,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -3667,12 +4540,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3681,17 +4554,17 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3699,11 +4572,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -3726,7 +4599,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -3736,15 +4609,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -3754,8 +4627,188 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
@@ -24,11 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
         <v>12</v>
@@ -666,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -816,17 +816,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -892,95 +892,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
+      <c r="K8" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1018,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: J. Bailey (40 L)</t>
+          <t>Maior volume: J. Bailey (61 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1120,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: J. Bailey (20 3PA)</t>
+          <t>Maior volume 3pt: J. Bailey (31 3PA)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: D. Carr (1.2 pts/shot)</t>
+          <t>Mais eficaz: D. Carr (1.1 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1144,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (42 L)</t>
+          <t>Zona mais usada: Above the Break 3 (73 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1156,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (52.8%)</t>
+          <t>Zona mais eficaz: Restricted Area (58.6%)</t>
         </is>
       </c>
     </row>
@@ -1215,34 +1305,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1250,11 +1340,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1263,18 +1353,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1292,66 +1382,66 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34.1%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>22</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>34.6%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1360,60 +1450,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1428,35 +1518,35 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1464,89 +1554,89 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1558,11 +1648,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1571,75 +1661,75 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1662,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1677,7 +1767,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1687,24 +1777,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1725,21 +1815,21 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1816,7 +1906,7 @@
         <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1831,7 +1921,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -1841,20 +1931,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1871,7 +1965,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1886,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -2037,431 +2131,431 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>12</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2484,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2602,29 +2696,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2632,11 +2726,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2658,29 +2752,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2688,7 +2782,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2714,29 +2808,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2744,186 +2838,186 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>85.7%</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>0.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2976,10 +3070,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3006,14 +3100,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -3024,18 +3118,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3050,25 +3144,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3086,7 +3184,9 @@
       <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
@@ -3100,7 +3200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3194,38 +3294,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3233,78 +3333,134 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
         <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>38</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>ESG_J._BAILEY</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>J. Bailey</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" t="n">
-        <v>27</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="C4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25.8%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>61</v>
+      </c>
+      <c r="H4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N4" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3383,32 +3539,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3418,25 +3574,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3453,13 +3609,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3471,14 +3627,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3488,7 +3644,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -3498,22 +3654,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3523,32 +3679,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3576,14 +3732,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3718,11 +3874,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3731,11 +3887,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3744,31 +3900,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -3788,7 +3944,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3801,73 +3957,73 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3884,89 +4040,89 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -3974,22 +4130,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3998,53 +4154,53 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>21</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -4054,12 +4210,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4068,11 +4224,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4090,11 +4246,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4102,15 +4258,15 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4118,7 +4274,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -4151,11 +4307,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4172,23 +4328,23 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>6</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="P8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -4287,7 +4443,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4298,23 +4454,37 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4419,32 +4589,32 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -4464,13 +4634,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4482,7 +4652,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4509,25 +4679,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4540,31 +4710,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4572,7 +4742,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4585,39 +4755,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4630,12 +4800,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4644,115 +4814,115 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4765,31 +4935,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4797,18 +4967,378 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11.4%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11.4%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ESG.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E2" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>12</v>
@@ -663,10 +663,10 @@
         <v>12</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -816,25 +816,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -847,31 +847,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,11 +879,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -902,33 +902,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -937,43 +937,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -982,95 +982,455 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25.8%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>0.7</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>34.4%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ESG_Z._JAMES</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Z. James</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1085,7 +1445,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,7 +1468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: J. Bailey (61 L)</t>
+          <t>Maior volume: J. Bailey (78 L)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: J. Bailey (31 3PA)</t>
+          <t>Maior volume 3pt: J. Bailey (41 3PA)</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1492,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: D. Carr (1.1 pts/shot)</t>
+          <t>Mais eficaz: D. Carr (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (73 L)</t>
+          <t>Zona mais usada: Above the Break 3 (109 L)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (58.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (60.0%)</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1305,30 +1665,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1340,11 +1700,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1353,11 +1713,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1382,7 +1742,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -1392,24 +1752,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1417,11 +1777,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1441,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1459,34 +1819,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>47.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>25</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>12</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1494,11 +1854,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1507,7 +1867,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1521,49 +1881,49 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1571,11 +1931,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1584,234 +1944,234 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>38.1%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>38.1%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_Z._JAMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>Z. James</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1819,59 +2179,59 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1879,97 +2239,97 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESG_F._NETO</t>
+          <t>ESG_M._POMBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1980,14 +2340,91 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESG_F._NETO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F. Neto</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="S10" t="n">
-        <v>9</v>
+      <c r="S11" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1998,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2131,33 +2568,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="H2" t="n">
-        <v>12</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2166,11 +2603,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2179,7 +2616,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -2208,21 +2645,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
         <v>6</v>
@@ -2234,40 +2671,40 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -2289,29 +2726,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2320,11 +2757,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2333,11 +2770,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2353,12 +2790,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2366,76 +2803,76 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>18</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2443,29 +2880,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2474,11 +2911,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2487,32 +2924,32 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2520,69 +2957,146 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
+        <v>38</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>52.1%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ESG_Z._JAMES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Z. James</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>6</v>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2593,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2696,26 +3210,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="I2" t="n">
         <v>0.9</v>
@@ -2726,11 +3240,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2743,38 +3257,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2782,55 +3296,55 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2838,257 +3352,257 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Z._JAMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Z. James</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>21</v>
-      </c>
-      <c r="H7" t="n">
-        <v>20</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_M._POMBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3100,51 +3614,51 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESG_F._NETO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -3156,17 +3670,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3174,11 +3688,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3188,8 +3702,64 @@
         <v>7</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESG_F._NETO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F. Neto</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3200,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3303,45 +3873,45 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>12</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -3359,29 +3929,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3389,11 +3959,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -3415,26 +3985,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="I4" t="n">
         <v>0.9</v>
@@ -3445,11 +4015,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -3459,8 +4029,120 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESG_Z._JAMES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Z. James</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3539,25 +4221,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3574,17 +4256,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3592,7 +4274,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3609,25 +4291,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3644,32 +4326,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3679,7 +4361,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -3689,22 +4371,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3714,7 +4396,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -3724,22 +4406,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3754,7 +4436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3765,7 +4447,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3874,11 +4556,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3887,11 +4569,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3900,27 +4582,27 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3944,11 +4626,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3966,35 +4648,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -4014,11 +4696,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4027,55 +4709,55 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4084,11 +4766,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4097,11 +4779,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4110,200 +4792,200 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_Z._JAMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>Z. James</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4311,16 +4993,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4328,34 +5010,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4364,131 +5046,201 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ESG_M._POMBO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>ESG_F._NETO</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>F. Neto</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
         <v>0.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4499,7 +5251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4589,17 +5341,17 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
         <v>21</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -4607,7 +5359,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4620,12 +5372,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4634,119 +5386,119 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -4787,14 +5539,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4814,25 +5566,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4845,271 +5597,271 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_Z._JAMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>Z. James</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11.5%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5129,52 +5881,52 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -5184,19 +5936,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -5205,12 +5957,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5219,7 +5971,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -5229,116 +5981,251 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>23.8%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ESG_Z._JAMES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Z. James</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>